--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487797_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487797_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1776</v>
+        <v>5.5317</v>
       </c>
       <c r="E2" t="n">
         <v>5.3505</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8272</v>
+        <v>0.1813</v>
       </c>
       <c r="G2" t="n">
         <v>1.7481</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5513</v>
+        <v>-0.0946</v>
       </c>
       <c r="T2" t="n">
         <v>0.2172</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3341</v>
+        <v>-0.3118</v>
       </c>
       <c r="V2" t="n">
         <v>4.0863</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9142</v>
+        <v>5.4603</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6371</v>
+        <v>2.0657</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2771</v>
+        <v>3.3945</v>
       </c>
       <c r="G3" t="n">
         <v>4.0318</v>
@@ -688,13 +688,13 @@
         <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.077</v>
+        <v>0.4691</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.0809</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4326</v>
+        <v>0.55</v>
       </c>
       <c r="V3" t="n">
         <v>1.1675</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6004</v>
+        <v>0.9281</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6167</v>
+        <v>0.9738</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0163</v>
+        <v>-0.0457</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6506999999999999</v>
@@ -766,13 +766,13 @@
         <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9806</v>
+        <v>0.3083</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1025</v>
+        <v>0.4596</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.122</v>
+        <v>-0.1513</v>
       </c>
       <c r="V4" t="n">
         <v>0.23</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7402</v>
+        <v>0.4292</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2903</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0305</v>
+        <v>0.4207</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6343</v>
+        <v>0.7319</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.6952</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7217</v>
+        <v>0.0367</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4791</v>
+        <v>-0.1048</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.431</v>
+        <v>0.6096</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0482</v>
+        <v>-0.7144</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1552</v>
+        <v>0.8367</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5183</v>
+        <v>0.0856</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6735</v>
+        <v>0.7511</v>
       </c>
       <c r="P5" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.0406</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3132</v>
+        <v>-0.3215</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0619</v>
+        <v>-0.1167</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2512</v>
+        <v>-0.2048</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0614</v>
+        <v>-0.8137</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1061</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6332</v>
+        <v>0.3013</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>-0.6117</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3032</v>
+        <v>0.9131</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7319</v>
+        <v>-0.6343</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6952</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0367</v>
+        <v>-0.7217</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1048</v>
+        <v>-0.4791</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6096</v>
+        <v>-0.431</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7144</v>
+        <v>-0.0482</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8367</v>
+        <v>-0.1552</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0856</v>
+        <v>0.5183</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7511</v>
+        <v>-0.6735</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1174</v>
+        <v>-0.1257</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2048</v>
+        <v>-0.2595</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3223</v>
+        <v>0.1338</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8137</v>
+        <v>1.0614</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0437</v>
+        <v>-0.1061</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4032</v>
+        <v>-0.0523</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4335</v>
+        <v>4.755</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.8367</v>
+        <v>-4.8073</v>
       </c>
       <c r="G7" t="n">
         <v>4.8696</v>
@@ -1000,13 +1000,13 @@
         <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6297</v>
+        <v>-1.2789</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5748</v>
+        <v>-0.2533</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0549</v>
+        <v>-1.0255</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9376</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1184</v>
+        <v>-1.8747</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.019</v>
+        <v>1.7602</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0993</v>
+        <v>-3.635</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8324</v>
+        <v>-0.0538</v>
       </c>
       <c r="H8" t="n">
-        <v>0.243</v>
+        <v>1.7741</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0753</v>
+        <v>-1.828</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2987</v>
+        <v>2.0323</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0635</v>
+        <v>1.5498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2351</v>
+        <v>0.4825</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.131</v>
+        <v>-2.0862</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1794</v>
+        <v>0.2243</v>
       </c>
       <c r="O8" t="n">
         <v>-2.3105</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4195</v>
+        <v>-0.7158</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0091</v>
+        <v>-0.0452</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4105</v>
+        <v>-0.6706</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1675</v>
+        <v>-1.5213</v>
       </c>
       <c r="W8" t="n">
-        <v>2.795</v>
+        <v>0.8137</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6275</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5485</v>
+        <v>-2.5191</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4388</v>
+        <v>-0.1262</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.9873</v>
+        <v>-2.3929</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0538</v>
+        <v>-1.8324</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7741</v>
+        <v>0.243</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.828</v>
+        <v>-2.0753</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0323</v>
+        <v>0.2987</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5498</v>
+        <v>0.0635</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4825</v>
+        <v>0.2351</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0862</v>
+        <v>-2.131</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2243</v>
+        <v>0.1794</v>
       </c>
       <c r="O9" t="n">
         <v>-2.3105</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3896</v>
+        <v>0.0188</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3667</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0229</v>
+        <v>0.1169</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5213</v>
+        <v>1.1675</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8137</v>
+        <v>2.795</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3351</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5767</v>
+        <v>-2.5958</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6513</v>
+        <v>-1.7585</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9253</v>
+        <v>-0.8373</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9988</v>
@@ -1234,13 +1234,13 @@
         <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>0.214</v>
+        <v>0.1949</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4534</v>
+        <v>0.3462</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2394</v>
+        <v>-0.1513</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5678</v>
+        <v>-3.7575</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7351</v>
+        <v>-2.3065</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8327</v>
+        <v>-1.451</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4146</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6558</v>
+        <v>-0.8455</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3667</v>
+        <v>0.0619</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2891</v>
+        <v>-0.9074</v>
       </c>
       <c r="V11" t="n">
         <v>1.1675</v>
@@ -1345,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.850999999999999</v>
+        <v>1.851200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1109</v>
+        <v>10.1108</v>
       </c>
       <c r="F12" t="n">
         <v>-8.259600000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>2.796799999999998</v>
+        <v>2.7968</v>
       </c>
       <c r="H12" t="n">
         <v>8.838199999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.041599999999999</v>
+        <v>-6.0416</v>
       </c>
       <c r="J12" t="n">
         <v>13.3709</v>
       </c>
       <c r="K12" t="n">
-        <v>8.227400000000001</v>
+        <v>8.227399999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>5.1433</v>
+        <v>5.143300000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-10.5741</v>
@@ -1393,10 +1393,10 @@
         <v>-2.3909</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2311000000000001</v>
+        <v>0.2312</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.6222</v>
+        <v>-2.622</v>
       </c>
       <c r="V12" t="n">
         <v>5.6076</v>
@@ -1405,7 +1405,7 @@
         <v>12.1174</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.5099</v>
+        <v>-6.509900000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.7985</v>
+        <v>6.8675</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4664</v>
+        <v>6.3592</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3322</v>
+        <v>0.5083</v>
       </c>
       <c r="G13" t="n">
         <v>5.2499</v>
@@ -1468,13 +1468,13 @@
         <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8161</v>
+        <v>0.8851</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9035</v>
+        <v>0.7963</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0888</v>
       </c>
       <c r="V13" t="n">
         <v>1.9813</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6956</v>
+        <v>3.7184</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0382</v>
+        <v>3.629</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3426</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7248</v>
+        <v>2.6195</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.631</v>
+        <v>0.1024</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9062</v>
+        <v>2.517</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8145</v>
+        <v>2.9584</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3734</v>
+        <v>0.3026</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1879</v>
+        <v>2.6558</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5393</v>
+        <v>-0.339</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2576</v>
+        <v>-0.2002</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2817</v>
+        <v>-0.1388</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>4.0905</v>
+        <v>1.0614</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8262</v>
+        <v>0.6706</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2643</v>
+        <v>0.3908</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.7513</v>
+        <v>-1.6275</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.1488</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2095</v>
+        <v>3.5293</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2004</v>
+        <v>4.6018</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0091</v>
+        <v>-1.0725</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6195</v>
+        <v>2.4172</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1024</v>
+        <v>-0.7489</v>
       </c>
       <c r="I15" t="n">
-        <v>2.517</v>
+        <v>3.1661</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9584</v>
+        <v>4.1604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3026</v>
+        <v>-0.2139</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6558</v>
+        <v>4.3743</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.339</v>
+        <v>-1.7432</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2002</v>
+        <v>-0.5349</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1388</v>
+        <v>-1.2083</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6649</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R15" t="n">
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5526</v>
+        <v>0.8176</v>
       </c>
       <c r="T15" t="n">
-        <v>0.242</v>
+        <v>0.4144</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3106</v>
+        <v>0.4032</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.6275</v>
+        <v>1.7513</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.1488</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6275</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5101</v>
+        <v>1.4063</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6374</v>
+        <v>1.9743</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1273</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4172</v>
+        <v>0.1718</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7489</v>
+        <v>-0.243</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1661</v>
+        <v>0.4147</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1604</v>
+        <v>1.8211</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2139</v>
+        <v>0.341</v>
       </c>
       <c r="L16" t="n">
-        <v>4.3743</v>
+        <v>1.4802</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7432</v>
+        <v>-1.6494</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5349</v>
+        <v>-0.5839</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2083</v>
+        <v>-1.0654</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6649</v>
+        <v>2.2893</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2016</v>
+        <v>0.2158</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.55</v>
+        <v>-0.2038</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3484</v>
+        <v>0.4195</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7513</v>
+        <v>-0.23</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1488</v>
+        <v>1.3975</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3975</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3959</v>
+        <v>1.3739</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2242</v>
+        <v>3.5736</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8283</v>
+        <v>-2.1997</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1718</v>
+        <v>-0.7248</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.243</v>
+        <v>-1.631</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4147</v>
+        <v>0.9062</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8211</v>
+        <v>0.8145</v>
       </c>
       <c r="K17" t="n">
-        <v>0.341</v>
+        <v>-0.3734</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4802</v>
+        <v>1.1879</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6494</v>
+        <v>-1.5393</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5839</v>
+        <v>-1.2576</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0654</v>
+        <v>-0.2817</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2893</v>
+        <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7946</v>
+        <v>1.7688</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9539</v>
+        <v>1.3616</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1592</v>
+        <v>0.4071</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
       <c r="W17" t="n">
         <v>1.3975</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6275</v>
+        <v>-3.1488</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6836</v>
+        <v>-2.4042</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.911</v>
+        <v>-2.8038</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2274</v>
+        <v>0.3996</v>
       </c>
       <c r="G18" t="n">
         <v>-2.8461</v>
@@ -1858,13 +1858,13 @@
         <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.67</v>
+        <v>-0.3906</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.261</v>
+        <v>-0.1538</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4091</v>
+        <v>-0.2368</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3246</v>
+        <v>-3.1376</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7948</v>
+        <v>-0.7158</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5299</v>
+        <v>-2.4219</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2074</v>
+        <v>-2.0523</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7209</v>
+        <v>-1.3836</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4866</v>
+        <v>-0.6686</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6992</v>
+        <v>0.381</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5816</v>
+        <v>0.3026</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1176</v>
+        <v>0.0784</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9066</v>
+        <v>-2.4332</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3025</v>
+        <v>-1.6862</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6041</v>
+        <v>-0.747</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1742</v>
+        <v>-0.3341</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2948</v>
+        <v>-0.0562</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1207</v>
+        <v>-0.2779</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8751</v>
+        <v>-1.1675</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-1.1675</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4567</v>
+        <v>-3.2698</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7158</v>
+        <v>-1.7948</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7409</v>
+        <v>-1.4751</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0523</v>
+        <v>-1.2074</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3836</v>
+        <v>-0.7209</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6686</v>
+        <v>-0.4866</v>
       </c>
       <c r="J20" t="n">
-        <v>0.381</v>
+        <v>0.6992</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3026</v>
+        <v>0.5816</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0784</v>
+        <v>0.1176</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4332</v>
+        <v>-1.9066</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6862</v>
+        <v>-1.3025</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.747</v>
+        <v>-0.6041</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4162</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6531</v>
+        <v>0.229</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0562</v>
+        <v>0.2948</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5969</v>
+        <v>-0.0659</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1675</v>
+        <v>-1.8751</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X20" t="n">
         <v>-1.1675</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.996</v>
+        <v>-8.5062</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.8854</v>
+        <v>-6.5639</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1106</v>
+        <v>-1.9423</v>
       </c>
       <c r="G21" t="n">
         <v>-6.4245</v>
@@ -2092,13 +2092,13 @@
         <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9232</v>
+        <v>-0.4334</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8234</v>
+        <v>-0.5019</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0998</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-2.6889</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8513</v>
+        <v>-0.4223999999999997</v>
       </c>
       <c r="E22" t="n">
-        <v>8.259599999999999</v>
+        <v>8.259600000000002</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.1109</v>
+        <v>-8.6822</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7967</v>
+        <v>-2.796699999999999</v>
       </c>
       <c r="H22" t="n">
         <v>-8.8384</v>
       </c>
       <c r="I22" t="n">
-        <v>6.041399999999999</v>
+        <v>6.0414</v>
       </c>
       <c r="J22" t="n">
         <v>10.5742</v>
@@ -2170,19 +2170,19 @@
         <v>15.6088</v>
       </c>
       <c r="S22" t="n">
-        <v>2.390899999999999</v>
+        <v>3.8196</v>
       </c>
       <c r="T22" t="n">
         <v>2.622</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2314000000000001</v>
+        <v>1.1973</v>
       </c>
       <c r="V22" t="n">
-        <v>-5.607699999999999</v>
+        <v>-5.6077</v>
       </c>
       <c r="W22" t="n">
-        <v>6.509899999999999</v>
+        <v>6.5099</v>
       </c>
       <c r="X22" t="n">
         <v>-12.1176</v>
